--- a/2 курс/Основы программной инженерии/lab 1/Requirements.xlsx
+++ b/2 курс/Основы программной инженерии/lab 1/Requirements.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipka23\ITMO\2 курс\Основы программной инженерии\lab 1\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE492B09-84FE-4AA8-A5F0-FFBADE3DA3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -18,10 +24,362 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="108">
+  <si>
+    <t>FREQ-1.1</t>
+  </si>
+  <si>
+    <t>FREQ-1.2</t>
+  </si>
+  <si>
+    <t>FREQ-1.3</t>
+  </si>
+  <si>
+    <t>FREQ-1.4</t>
+  </si>
+  <si>
+    <t>FREQ-2.1</t>
+  </si>
+  <si>
+    <t>FREQ-2.2</t>
+  </si>
+  <si>
+    <t>FREQ-2.3</t>
+  </si>
+  <si>
+    <t>FREQ-2.4</t>
+  </si>
+  <si>
+    <t>FREQ-2.5</t>
+  </si>
+  <si>
+    <t>FREQ-2.6</t>
+  </si>
+  <si>
+    <t>FREQ-2.7</t>
+  </si>
+  <si>
+    <t>FREQ-3.1</t>
+  </si>
+  <si>
+    <t>FREQ-3.2</t>
+  </si>
+  <si>
+    <t>FREQ-4.1</t>
+  </si>
+  <si>
+    <t>FREQ-4.2</t>
+  </si>
+  <si>
+    <t>FREQ-5.1</t>
+  </si>
+  <si>
+    <t>FREQ-5.2</t>
+  </si>
+  <si>
+    <t>FREQ-5.3</t>
+  </si>
+  <si>
+    <t>FREQ-5.4</t>
+  </si>
+  <si>
+    <t>FREQ-6.1</t>
+  </si>
+  <si>
+    <t>FREQ-6.2</t>
+  </si>
+  <si>
+    <t>FREQ-6.3</t>
+  </si>
+  <si>
+    <t>FREQ-6.4</t>
+  </si>
+  <si>
+    <t>FREQ-7.1</t>
+  </si>
+  <si>
+    <t>FREQ-7.2</t>
+  </si>
+  <si>
+    <t>FREQ-7.3</t>
+  </si>
+  <si>
+    <t>FREQ-7.4</t>
+  </si>
+  <si>
+    <t>FREQ-7.5</t>
+  </si>
+  <si>
+    <t>FREQ-7.6</t>
+  </si>
+  <si>
+    <t>FREQ-8.1</t>
+  </si>
+  <si>
+    <t>FREQ-8.2</t>
+  </si>
+  <si>
+    <t>FREQ-8.3</t>
+  </si>
+  <si>
+    <t>FREQ-8.4</t>
+  </si>
+  <si>
+    <t>FREQ-8.5</t>
+  </si>
+  <si>
+    <t>FREQ-8.6</t>
+  </si>
+  <si>
+    <t>FREQ-9.1</t>
+  </si>
+  <si>
+    <t>FREQ-9.2</t>
+  </si>
+  <si>
+    <t>FREQ-9.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">№ требования  </t>
+  </si>
+  <si>
+    <t>Приоритетность</t>
+  </si>
+  <si>
+    <t>Трудоемкость
+человеко-час</t>
+  </si>
+  <si>
+    <t>Стабильность</t>
+  </si>
+  <si>
+    <t>NFREQ-1.1</t>
+  </si>
+  <si>
+    <t>NFREQ-1.2</t>
+  </si>
+  <si>
+    <t>NFREQ-2.1</t>
+  </si>
+  <si>
+    <t>NFREQ-3.1</t>
+  </si>
+  <si>
+    <t>NFREQ-3.2</t>
+  </si>
+  <si>
+    <t>NFREQ-4.1</t>
+  </si>
+  <si>
+    <t>NFREQ-4.2</t>
+  </si>
+  <si>
+    <t>NFREQ-5.1</t>
+  </si>
+  <si>
+    <t>NFREQ-5.2</t>
+  </si>
+  <si>
+    <t>Требование</t>
+  </si>
+  <si>
+    <t>Высокая</t>
+  </si>
+  <si>
+    <t>FREQ-1.1: Система позволяет авторизованному пользователю загрузить видео на свой канал.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-1.2: Система позволяет пользователю указать название, описание, категорию и тип доступа (для всех/по ссылке) видео.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-1.3: Система позволяет загрузить обложку для видео.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-1.4: При некорректных данных система показывает сообщение об ошибке и не сохраняет изменения.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-2.1: Система позволяет любому пользователю воспроизвести видео.[support.google]​</t>
+  </si>
+  <si>
+    <t>FREQ-2.2: Система позволяет изменять качество видео от 144p до 4K с помощью кнопок в плеере.[support.google]​</t>
+  </si>
+  <si>
+    <t>FREQ-2.3: Система позволяет воспроизводить видео в полноэкранном режиме.[support.google]​</t>
+  </si>
+  <si>
+    <t>FREQ-2.4: Система позволяет изменять скорость воспроизведения видео от 0.25x до 2x с шагом 0.25.[support.google]​</t>
+  </si>
+  <si>
+    <t>FREQ-2.5: Система позволяет включить субтитры с помощью кнопки в плеере.[support.google]​</t>
+  </si>
+  <si>
+    <t>FREQ-2.6: Система позволяет перематывать видео на 10 секунд назад и вперед по кнопкам в плеере.[support.google]​</t>
+  </si>
+  <si>
+    <t>FREQ-2.7: Система поддерживает одновременную загрузку нескольких видеороликов.[support.google]​</t>
+  </si>
+  <si>
+    <t>FREQ-3.1: Система выдает 10 подсказок при вводе в поисковую строку не менее 2 символов.[machineheads]​</t>
+  </si>
+  <si>
+    <t>FREQ-3.2: Результат поиска — страница с прокручивающейся лентой видео и каналов.[machineheads]​</t>
+  </si>
+  <si>
+    <t>FREQ-4.1: Система должна показывать авторизованному пользователю персонализированную ленту рекомендаций на основе его интересов.[utify]​</t>
+  </si>
+  <si>
+    <t>FREQ-4.2: Система должна показывать неавторизованному пользователю персонализированную ленту рекомендаций, формируемую алгоритмом по популярности и трендам.[utify]​</t>
+  </si>
+  <si>
+    <t>FREQ-5.1: Под каждым видео есть счетчик лайков и дизлайков.[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-5.2: Под каждым видео есть секция с комментариями и полем ввода для новых комментариев.[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-5.3: Система позволяет авторизованным пользователям ставить оценку к видео (лайк/дизлайк), а неавторизованных при попытке оставить оценку перенаправляет на страницу авторизации.[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-5.4: Система позволяет авторизованным пользователям отправлять комментарии, неавторизованным показывается сообщение «Войдите, чтобы комментировать».[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-6.1: У каждого канала есть кнопка подписки.[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-6.2: При повторном нажатии на кнопку подписки производится отписка.[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-6.3: При подписке увеличивается счетчик подписчиков.[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-6.4: Система позволяет авторизованным пользователям подписываться на каналы других пользователей, а неавторизованных при попытке подписаться перенаправляет на страницу авторизации.[rasshifrui]​</t>
+  </si>
+  <si>
+    <t>FREQ-7.1: Система позволяет авторизованному пользователю создавать плейлист.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-7.2: Система позволяет авторизованному пользователю добавлять в свой плейлист любые свои видео, доступные в его студии Rutube.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-7.3: Система позволяет авторизованному пользователю удалять из своего плейлиста любое ранее добавленное видео.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-7.4: Система позволяет авторизованному пользователю подписываться на плейлист другого пользователя, чтобы он отображался в его списке плейлистов для быстрого доступа.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-7.5: Система позволяет пользователю указать название и описание для плейлиста.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-7.6: Система позволяет загрузить обложку для плейлиста.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-8.1: Система позволяет владельцу канала загрузить и изменить аватар канала.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-8.2: Система позволяет владельцу канала загрузить и изменить обложку канала.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-8.3: Система позволяет владельцу канала задать и изменить название и описание канала.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-8.4: При отсутствии загруженного аватара система показывает стандартную иконку канала.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-8.5: При отсутствии загруженной обложки система показывает стандартный фон канала.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-8.6: При некорректных данных система показывает сообщение об ошибке и не сохраняет изменения.[xn----dtbhaacat8bfloi8h]​</t>
+  </si>
+  <si>
+    <t>FREQ-9.1: Система позволяет пользователю указать название и описание для трансляции.[machineheads]​</t>
+  </si>
+  <si>
+    <t>FREQ-9.2: Система позволяет загрузить обложку для трансляции.[machineheads]​</t>
+  </si>
+  <si>
+    <t>FREQ-9.3: Только авторизованный пользователь может запустить трансляцию, неавторизованных перенаправляет на страницу авторизации.[machineheads]</t>
+  </si>
+  <si>
+    <t>40+</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Средняя</t>
+  </si>
+  <si>
+    <t>16-40</t>
+  </si>
+  <si>
+    <t>4-16</t>
+  </si>
+  <si>
+    <t>&lt;4</t>
+  </si>
+  <si>
+    <t>Низкая</t>
+  </si>
+  <si>
+    <t>NFREQ-1.1: Время загрузки страницы просмотра видео не должно превышать 2 секунд при стабильном подключении к интернету</t>
+  </si>
+  <si>
+    <t>NFREQ-1.2: Плеер должен начинать воспроизведение выбранного видео не позднее чем через 3 секунды после нажатия на него</t>
+  </si>
+  <si>
+    <t>NFREQ-2.1: В случае ошибки загрузки видео не публикуется</t>
+  </si>
+  <si>
+    <t>NFREQ-3.1: Доступ к управлению каналом должен предоставляться только авторизованным пользователям по защищённому протоколу HTTPS.</t>
+  </si>
+  <si>
+    <t>NFREQ-3.2: Приватные видео и плейлисты должны быть доступны только их владельцу или пользователям с выданными правами доступа.</t>
+  </si>
+  <si>
+    <t>NFREQ-4.1: Интерфейс быть интуитивно понятен пользователю без предварительного обучения</t>
+  </si>
+  <si>
+    <t>NFREQ-4.2: Система должна быть доступна в любое время</t>
+  </si>
+  <si>
+    <t>NFREQ-5.1: Пользователь может загружать не более 5 видеороликов одновременно</t>
+  </si>
+  <si>
+    <t>NFREQ-5.2: Монетизация канала доступна при достижении 20 000 просмотров в сумме за все видео на канале</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -37,7 +395,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +403,48 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +721,858 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A2:H54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="5" width="15.7109375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="9.140625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="5">
+        <v>10</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>10</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="5">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="5">
+        <v>10</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="5">
+        <v>10</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>6</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>7</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="5">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="5">
+        <v>10</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="5">
+        <v>7</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="5">
+        <v>7</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="5">
+        <v>9</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="5">
+        <v>9</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="5">
+        <v>9</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="5">
+        <v>9</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" s="5">
+        <v>9</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="5">
+        <v>9</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C24" s="5">
+        <v>9</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="5">
+        <v>9</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="5">
+        <v>2</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" s="5">
+        <v>2</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="5">
+        <v>2</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C29" s="5">
+        <v>2</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="5">
+        <v>2</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="5">
+        <v>2</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="5">
+        <v>8</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C33" s="5">
+        <v>7</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="5">
+        <v>6</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="5">
+        <v>4</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="5">
+        <v>4</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="5">
+        <v>8</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C38" s="5">
+        <v>5</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B39" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="5">
+        <v>5</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C40" s="5">
+        <v>5</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H45"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B46" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B47" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F47" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B48" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F50" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F51" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F52" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F53" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F54" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F3" r:id="rId1" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{8F8B7AB2-E1C9-4A13-BAEF-C5ACB1451C39}"/>
+    <hyperlink ref="F4" r:id="rId2" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{597B2B20-EF3D-43E8-9E8A-69977F34AD5E}"/>
+    <hyperlink ref="F5" r:id="rId3" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{1E607B17-E646-4092-A4AB-1F80FAFF6FDF}"/>
+    <hyperlink ref="F6" r:id="rId4" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{ABF60D73-EB41-4775-990C-58A3FB11F47A}"/>
+    <hyperlink ref="F7" r:id="rId5" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{6A005603-E00E-401F-B10D-F4F0C6B16B4C}"/>
+    <hyperlink ref="F8" r:id="rId6" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{70AD2B7F-C0D6-427B-9381-C37279E4C44C}"/>
+    <hyperlink ref="F9" r:id="rId7" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{02B7D14F-9D3A-447C-81DD-61714F2AF976}"/>
+    <hyperlink ref="F10" r:id="rId8" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{63BB239A-9056-4996-A357-2350292BCB59}"/>
+    <hyperlink ref="F11" r:id="rId9" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{E3B321A0-7DC8-4347-9F7F-BA31EC6F9F62}"/>
+    <hyperlink ref="F12" r:id="rId10" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{861EBD53-CC2D-4201-89E9-8C34E94FCBC3}"/>
+    <hyperlink ref="F13" r:id="rId11" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{EF80A1CF-DF79-481F-B1EF-0F28D0122516}"/>
+    <hyperlink ref="F14" r:id="rId12" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{CF466025-DC60-439A-93FF-210317E9954A}"/>
+    <hyperlink ref="F15" r:id="rId13" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{98B4A9DA-B1C2-48E3-9F19-F051260F8EF3}"/>
+    <hyperlink ref="F16" r:id="rId14" display="https://utify.io/ru/25-instrumentov-dlya-youtube" xr:uid="{90D89E95-90CB-4D9C-B0BD-3A1AABE751DF}"/>
+    <hyperlink ref="F17" r:id="rId15" display="https://utify.io/ru/25-instrumentov-dlya-youtube" xr:uid="{28D6E7BA-207F-4E36-A09B-06AF2FAE47A2}"/>
+    <hyperlink ref="F18" r:id="rId16" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{EF63269F-D0EE-4300-A83C-4AC87C6CC008}"/>
+    <hyperlink ref="F19" r:id="rId17" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{35A222E7-3160-4A21-B515-F94DB909DCB3}"/>
+    <hyperlink ref="F20" r:id="rId18" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{FBBE6079-5521-4891-A6BE-1B57D7E2DA34}"/>
+    <hyperlink ref="F21" r:id="rId19" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{9227A4F0-33F9-496B-8DD1-CF21416DA724}"/>
+    <hyperlink ref="F22" r:id="rId20" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{0BFD3088-3CAC-4844-B266-B44B5B7131BF}"/>
+    <hyperlink ref="F23" r:id="rId21" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{74ACF4B0-F387-490E-8CB6-1E4850362370}"/>
+    <hyperlink ref="F24" r:id="rId22" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{503EA185-FCCB-41A7-885C-71E73A04AB9A}"/>
+    <hyperlink ref="F25" r:id="rId23" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{226BE699-9552-4816-A526-0F69F153C3A1}"/>
+    <hyperlink ref="F26" r:id="rId24" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{54F5C5ED-1CD1-407B-A121-F98430F9231E}"/>
+    <hyperlink ref="F27" r:id="rId25" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{BABB8466-709E-49BD-B4DB-E36BB8AF50FE}"/>
+    <hyperlink ref="F28" r:id="rId26" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{828F1020-6C0E-4A20-A6AD-F4083DA67E26}"/>
+    <hyperlink ref="F29" r:id="rId27" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{1C3CEFCB-A1F9-4E6D-97EE-F30CCB1D23E5}"/>
+    <hyperlink ref="F30" r:id="rId28" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{4E8F8030-59AC-455B-9F55-3D7758A46DE8}"/>
+    <hyperlink ref="F31" r:id="rId29" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{E43BC458-FBCD-4DFD-8524-400856E04736}"/>
+    <hyperlink ref="F32" r:id="rId30" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{F561C96D-FFEF-4CE3-995C-676FF79A39BE}"/>
+    <hyperlink ref="F33" r:id="rId31" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{7BBBFB92-1C0F-4228-8A71-E15B51B2E844}"/>
+    <hyperlink ref="F34" r:id="rId32" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{A06989E7-65A1-4762-8DB1-EF35A0A3E309}"/>
+    <hyperlink ref="F35" r:id="rId33" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{FC08E9C4-3472-4BB5-B06D-CE56BDA49A8F}"/>
+    <hyperlink ref="F36" r:id="rId34" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{E29FFDEF-71B7-493E-A901-F5AA1705C04E}"/>
+    <hyperlink ref="F37" r:id="rId35" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{A0278046-E4DE-4EBD-BE12-6D26781D587B}"/>
+    <hyperlink ref="F38" r:id="rId36" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{3AE8D3DA-0150-4006-8A87-623FCBC6071F}"/>
+    <hyperlink ref="F39" r:id="rId37" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{607CB8F8-D5BA-467A-B87B-78C9C15A279E}"/>
+    <hyperlink ref="F40" r:id="rId38" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{063CCAAE-A296-4A09-BEFB-A486892AE4DB}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2 курс/Основы программной инженерии/lab 1/Requirements.xlsx
+++ b/2 курс/Основы программной инженерии/lab 1/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10908"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipka23\ITMO\2 курс\Основы программной инженерии\lab 1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ipka23/ITMO/2 курс/Основы программной инженерии/lab 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE492B09-84FE-4AA8-A5F0-FFBADE3DA3A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BD4990-B565-654F-8CE3-DF7CA42CF2A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="109">
   <si>
     <t>FREQ-1.1</t>
   </si>
@@ -350,13 +350,16 @@
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>FREQ-2.8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -386,6 +389,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -395,7 +410,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -418,12 +433,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -440,6 +468,18 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -722,18 +762,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:H55"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="2"/>
-    <col min="2" max="5" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="2"/>
-    <col min="7" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="9.140625" style="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="9.1640625" style="2"/>
+    <col min="2" max="5" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.1640625" style="2"/>
+    <col min="7" max="15" width="9.1640625" style="1"/>
+    <col min="16" max="16" width="9.1640625" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:6" ht="32" x14ac:dyDescent="0.2">
       <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
@@ -747,7 +787,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B3" s="4" t="s">
         <v>0</v>
       </c>
@@ -764,7 +804,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
@@ -781,7 +821,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -798,7 +838,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -815,7 +855,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
@@ -832,7 +872,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
@@ -849,7 +889,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -866,7 +906,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
@@ -883,7 +923,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
@@ -900,7 +940,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
         <v>9</v>
       </c>
@@ -917,7 +957,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
         <v>10</v>
       </c>
@@ -934,60 +974,58 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+    <row r="14" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B14" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C14" s="10">
+        <v>10</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B15" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C15" s="8">
         <v>1</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="4" t="s">
+      <c r="D15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
+    <row r="16" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C16" s="5">
         <v>10</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="5">
-        <v>7</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>94</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="5">
         <v>7</v>
@@ -999,46 +1037,46 @@
         <v>97</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="5">
+        <v>7</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="4" t="s">
+    <row r="19" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B19" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="C18" s="5">
-        <v>9</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="C19" s="5">
         <v>9</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B20" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5">
         <v>9</v>
@@ -1050,12 +1088,12 @@
         <v>52</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="5">
         <v>9</v>
@@ -1067,46 +1105,46 @@
         <v>52</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="5">
         <v>9</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C23" s="5">
         <v>9</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C24" s="5">
         <v>9</v>
@@ -1118,46 +1156,46 @@
         <v>52</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25" s="5">
         <v>9</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" s="5">
+        <v>9</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="4" t="s">
+    <row r="27" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B27" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="C26" s="5">
-        <v>2</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="4" t="s">
-        <v>24</v>
       </c>
       <c r="C27" s="5">
         <v>2</v>
@@ -1166,15 +1204,15 @@
         <v>95</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C28" s="5">
         <v>2</v>
@@ -1186,12 +1224,12 @@
         <v>93</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B29" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C29" s="5">
         <v>2</v>
@@ -1200,32 +1238,32 @@
         <v>95</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B30" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C30" s="5">
         <v>2</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="5">
         <v>2</v>
@@ -1237,80 +1275,80 @@
         <v>52</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="5">
+        <v>2</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="4" t="s">
+    <row r="33" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B33" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C33" s="5">
         <v>8</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="D33" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="4" t="s">
+    <row r="34" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B34" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C34" s="5">
         <v>7</v>
       </c>
-      <c r="D33" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="D34" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="4" t="s">
+    <row r="35" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B35" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C35" s="5">
         <v>6</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="5">
-        <v>4</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>96</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B36" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C36" s="5">
         <v>4</v>
@@ -1322,63 +1360,63 @@
         <v>93</v>
       </c>
       <c r="F36" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B37" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="5">
+        <v>4</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B37" s="4" t="s">
+    <row r="38" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B38" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C38" s="5">
         <v>8</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F37" s="3" t="s">
+      <c r="D38" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B38" s="4" t="s">
+    <row r="39" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B39" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="C38" s="5">
-        <v>5</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B39" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="C39" s="5">
         <v>5</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B40" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C40" s="5">
         <v>5</v>
@@ -1390,38 +1428,41 @@
         <v>52</v>
       </c>
       <c r="F40" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B41" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C41" s="5">
+        <v>5</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="45" spans="2:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="B45" s="4" t="s">
+    <row r="46" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B46" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C46" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D46" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="H45"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B46" s="4" t="s">
+      <c r="H46"/>
+    </row>
+    <row r="47" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="B47" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F46" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B47" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>107</v>
@@ -1430,12 +1471,12 @@
         <v>52</v>
       </c>
       <c r="F47" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="16" x14ac:dyDescent="0.2">
       <c r="B48" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>107</v>
@@ -1444,12 +1485,12 @@
         <v>52</v>
       </c>
       <c r="F48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B49" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>107</v>
@@ -1458,12 +1499,12 @@
         <v>52</v>
       </c>
       <c r="F49" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B50" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>107</v>
@@ -1472,12 +1513,12 @@
         <v>52</v>
       </c>
       <c r="F50" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B51" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>107</v>
@@ -1486,12 +1527,12 @@
         <v>52</v>
       </c>
       <c r="F51" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B52" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>107</v>
@@ -1500,26 +1541,26 @@
         <v>52</v>
       </c>
       <c r="F52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B53" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="4" t="s">
+    <row r="54" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B54" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F53" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
-        <v>50</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>92</v>
@@ -1528,6 +1569,20 @@
         <v>97</v>
       </c>
       <c r="F54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B55" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F55" t="s">
         <v>106</v>
       </c>
     </row>
@@ -1545,33 +1600,33 @@
     <hyperlink ref="F11" r:id="rId9" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{E3B321A0-7DC8-4347-9F7F-BA31EC6F9F62}"/>
     <hyperlink ref="F12" r:id="rId10" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{861EBD53-CC2D-4201-89E9-8C34E94FCBC3}"/>
     <hyperlink ref="F13" r:id="rId11" display="https://support.google.com/youtube/answer/1722171?hl=ru" xr:uid="{EF80A1CF-DF79-481F-B1EF-0F28D0122516}"/>
-    <hyperlink ref="F14" r:id="rId12" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{CF466025-DC60-439A-93FF-210317E9954A}"/>
-    <hyperlink ref="F15" r:id="rId13" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{98B4A9DA-B1C2-48E3-9F19-F051260F8EF3}"/>
-    <hyperlink ref="F16" r:id="rId14" display="https://utify.io/ru/25-instrumentov-dlya-youtube" xr:uid="{90D89E95-90CB-4D9C-B0BD-3A1AABE751DF}"/>
-    <hyperlink ref="F17" r:id="rId15" display="https://utify.io/ru/25-instrumentov-dlya-youtube" xr:uid="{28D6E7BA-207F-4E36-A09B-06AF2FAE47A2}"/>
-    <hyperlink ref="F18" r:id="rId16" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{EF63269F-D0EE-4300-A83C-4AC87C6CC008}"/>
-    <hyperlink ref="F19" r:id="rId17" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{35A222E7-3160-4A21-B515-F94DB909DCB3}"/>
-    <hyperlink ref="F20" r:id="rId18" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{FBBE6079-5521-4891-A6BE-1B57D7E2DA34}"/>
-    <hyperlink ref="F21" r:id="rId19" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{9227A4F0-33F9-496B-8DD1-CF21416DA724}"/>
-    <hyperlink ref="F22" r:id="rId20" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{0BFD3088-3CAC-4844-B266-B44B5B7131BF}"/>
-    <hyperlink ref="F23" r:id="rId21" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{74ACF4B0-F387-490E-8CB6-1E4850362370}"/>
-    <hyperlink ref="F24" r:id="rId22" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{503EA185-FCCB-41A7-885C-71E73A04AB9A}"/>
-    <hyperlink ref="F25" r:id="rId23" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{226BE699-9552-4816-A526-0F69F153C3A1}"/>
-    <hyperlink ref="F26" r:id="rId24" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{54F5C5ED-1CD1-407B-A121-F98430F9231E}"/>
-    <hyperlink ref="F27" r:id="rId25" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{BABB8466-709E-49BD-B4DB-E36BB8AF50FE}"/>
-    <hyperlink ref="F28" r:id="rId26" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{828F1020-6C0E-4A20-A6AD-F4083DA67E26}"/>
-    <hyperlink ref="F29" r:id="rId27" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{1C3CEFCB-A1F9-4E6D-97EE-F30CCB1D23E5}"/>
-    <hyperlink ref="F30" r:id="rId28" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{4E8F8030-59AC-455B-9F55-3D7758A46DE8}"/>
-    <hyperlink ref="F31" r:id="rId29" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{E43BC458-FBCD-4DFD-8524-400856E04736}"/>
-    <hyperlink ref="F32" r:id="rId30" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{F561C96D-FFEF-4CE3-995C-676FF79A39BE}"/>
-    <hyperlink ref="F33" r:id="rId31" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{7BBBFB92-1C0F-4228-8A71-E15B51B2E844}"/>
-    <hyperlink ref="F34" r:id="rId32" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{A06989E7-65A1-4762-8DB1-EF35A0A3E309}"/>
-    <hyperlink ref="F35" r:id="rId33" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{FC08E9C4-3472-4BB5-B06D-CE56BDA49A8F}"/>
-    <hyperlink ref="F36" r:id="rId34" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{E29FFDEF-71B7-493E-A901-F5AA1705C04E}"/>
-    <hyperlink ref="F37" r:id="rId35" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{A0278046-E4DE-4EBD-BE12-6D26781D587B}"/>
-    <hyperlink ref="F38" r:id="rId36" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{3AE8D3DA-0150-4006-8A87-623FCBC6071F}"/>
-    <hyperlink ref="F39" r:id="rId37" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{607CB8F8-D5BA-467A-B87B-78C9C15A279E}"/>
-    <hyperlink ref="F40" r:id="rId38" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{063CCAAE-A296-4A09-BEFB-A486892AE4DB}"/>
+    <hyperlink ref="F15" r:id="rId12" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{CF466025-DC60-439A-93FF-210317E9954A}"/>
+    <hyperlink ref="F16" r:id="rId13" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{98B4A9DA-B1C2-48E3-9F19-F051260F8EF3}"/>
+    <hyperlink ref="F17" r:id="rId14" display="https://utify.io/ru/25-instrumentov-dlya-youtube" xr:uid="{90D89E95-90CB-4D9C-B0BD-3A1AABE751DF}"/>
+    <hyperlink ref="F18" r:id="rId15" display="https://utify.io/ru/25-instrumentov-dlya-youtube" xr:uid="{28D6E7BA-207F-4E36-A09B-06AF2FAE47A2}"/>
+    <hyperlink ref="F19" r:id="rId16" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{EF63269F-D0EE-4300-A83C-4AC87C6CC008}"/>
+    <hyperlink ref="F20" r:id="rId17" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{35A222E7-3160-4A21-B515-F94DB909DCB3}"/>
+    <hyperlink ref="F21" r:id="rId18" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{FBBE6079-5521-4891-A6BE-1B57D7E2DA34}"/>
+    <hyperlink ref="F22" r:id="rId19" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{9227A4F0-33F9-496B-8DD1-CF21416DA724}"/>
+    <hyperlink ref="F23" r:id="rId20" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{0BFD3088-3CAC-4844-B266-B44B5B7131BF}"/>
+    <hyperlink ref="F24" r:id="rId21" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{74ACF4B0-F387-490E-8CB6-1E4850362370}"/>
+    <hyperlink ref="F25" r:id="rId22" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{503EA185-FCCB-41A7-885C-71E73A04AB9A}"/>
+    <hyperlink ref="F26" r:id="rId23" display="https://rasshifrui.ru/kak-pisat-funktsionalnye-trebovaniya-khabr/" xr:uid="{226BE699-9552-4816-A526-0F69F153C3A1}"/>
+    <hyperlink ref="F27" r:id="rId24" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{54F5C5ED-1CD1-407B-A121-F98430F9231E}"/>
+    <hyperlink ref="F28" r:id="rId25" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{BABB8466-709E-49BD-B4DB-E36BB8AF50FE}"/>
+    <hyperlink ref="F29" r:id="rId26" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{828F1020-6C0E-4A20-A6AD-F4083DA67E26}"/>
+    <hyperlink ref="F30" r:id="rId27" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{1C3CEFCB-A1F9-4E6D-97EE-F30CCB1D23E5}"/>
+    <hyperlink ref="F31" r:id="rId28" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{4E8F8030-59AC-455B-9F55-3D7758A46DE8}"/>
+    <hyperlink ref="F32" r:id="rId29" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{E43BC458-FBCD-4DFD-8524-400856E04736}"/>
+    <hyperlink ref="F33" r:id="rId30" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{F561C96D-FFEF-4CE3-995C-676FF79A39BE}"/>
+    <hyperlink ref="F34" r:id="rId31" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{7BBBFB92-1C0F-4228-8A71-E15B51B2E844}"/>
+    <hyperlink ref="F35" r:id="rId32" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{A06989E7-65A1-4762-8DB1-EF35A0A3E309}"/>
+    <hyperlink ref="F36" r:id="rId33" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{FC08E9C4-3472-4BB5-B06D-CE56BDA49A8F}"/>
+    <hyperlink ref="F37" r:id="rId34" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{E29FFDEF-71B7-493E-A901-F5AA1705C04E}"/>
+    <hyperlink ref="F38" r:id="rId35" display="https://решение-верное.рф/109-Requirements-3" xr:uid="{A0278046-E4DE-4EBD-BE12-6D26781D587B}"/>
+    <hyperlink ref="F39" r:id="rId36" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{3AE8D3DA-0150-4006-8A87-623FCBC6071F}"/>
+    <hyperlink ref="F40" r:id="rId37" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{607CB8F8-D5BA-467A-B87B-78C9C15A279E}"/>
+    <hyperlink ref="F41" r:id="rId38" display="https://machineheads.ru/blog/ustoychivyy-fundament-kak-svyazat-funktsionalnye-i-nefunktsionalnye-trebovaniya/" xr:uid="{063CCAAE-A296-4A09-BEFB-A486892AE4DB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2 курс/Основы программной инженерии/lab 1/Requirements.xlsx
+++ b/2 курс/Основы программной инженерии/lab 1/Requirements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10908"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ipka23/ITMO/2 курс/Основы программной инженерии/lab 1/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipka23\ITMO\2 курс\Основы программной инженерии\lab 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB6B9F4-7E64-0344-A899-89D73C29DD2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627089ED-46E6-4F00-A36C-48107E99A809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="740" windowWidth="28320" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="238">
   <si>
     <t xml:space="preserve">№ требования  </t>
   </si>
@@ -771,12 +771,106 @@
   <si>
     <t>14. Система добавляет плейлист в список плейлистов пользователя в студии Rutube.</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">FR-10.1: Система позволяет авторизованному пользователю оформить </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>платную подписку</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> с </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <u/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t>автопродлением</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> каждый месяц на сервис для дополнительных функций</t>
+    </r>
+  </si>
+  <si>
+    <t>FR-10.2: Система позволяет пользователю просмотреть статус своей подписки и дату следующего списания</t>
+  </si>
+  <si>
+    <t>FR-10.3: Система позволяет пользователю отменить автопродление подписки</t>
+  </si>
+  <si>
+    <t>FR-11.1: Система позволяет неавторизованному пользователю зарегистрироваться или войти в существующий аккаунт</t>
+  </si>
+  <si>
+    <t>FR-12.1: Система позволяет владельцу удалять видео с сайта</t>
+  </si>
+  <si>
+    <t>FR-12.2: Система позволяет владельцу менять права доступа пользователей к сайту</t>
+  </si>
+  <si>
+    <t>FR-12.3: Система позволяет владельцу изменять глобальные настройки сервиса</t>
+  </si>
+  <si>
+    <t>FR-10.1</t>
+  </si>
+  <si>
+    <t>FR-10.2</t>
+  </si>
+  <si>
+    <t>FR-10.3</t>
+  </si>
+  <si>
+    <t>FR-11.1</t>
+  </si>
+  <si>
+    <t>FR-12.1</t>
+  </si>
+  <si>
+    <t>FR-12.2</t>
+  </si>
+  <si>
+    <t>FR-12.3</t>
+  </si>
+  <si>
+    <t>FR-11.2: Система позволяет авторизованному пользователю выйти из аккаунта</t>
+  </si>
+  <si>
+    <t>FR-11.2</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -830,6 +924,29 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <u/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -867,7 +984,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -934,6 +1051,13 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1216,18 +1340,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:W61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <dimension ref="A2:W78"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1640625" style="8"/>
-    <col min="2" max="5" width="15.6640625" style="8" customWidth="1"/>
-    <col min="6" max="6" width="9.1640625" style="8"/>
-    <col min="7" max="15" width="9.1640625" style="3"/>
-    <col min="16" max="16" width="9.1640625" style="3" customWidth="1"/>
-    <col min="17" max="16384" width="9.1640625" style="3"/>
+    <col min="1" max="1" width="9.140625" style="8"/>
+    <col min="2" max="5" width="15.7109375" style="8" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="8"/>
+    <col min="7" max="15" width="9.140625" style="3"/>
+    <col min="16" max="16" width="9.140625" style="3" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" ht="30" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:23" ht="30" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
         <v>0</v>
       </c>
@@ -1245,7 +1369,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>17</v>
       </c>
@@ -1266,7 +1390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B4" s="9" t="s">
         <v>19</v>
       </c>
@@ -1287,7 +1411,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
@@ -1308,7 +1432,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B6" s="9" t="s">
         <v>23</v>
       </c>
@@ -1326,7 +1450,7 @@
       </c>
       <c r="G6" s="11"/>
     </row>
-    <row r="7" spans="2:23" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:23" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>98</v>
       </c>
@@ -1342,7 +1466,7 @@
       <c r="F7" s="10"/>
       <c r="G7" s="11"/>
     </row>
-    <row r="8" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
         <v>25</v>
       </c>
@@ -1360,7 +1484,7 @@
       </c>
       <c r="G8" s="11"/>
     </row>
-    <row r="9" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B9" s="9" t="s">
         <v>27</v>
       </c>
@@ -1378,7 +1502,7 @@
       </c>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B10" s="9" t="s">
         <v>29</v>
       </c>
@@ -1396,7 +1520,7 @@
       </c>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B11" s="9" t="s">
         <v>31</v>
       </c>
@@ -1414,7 +1538,7 @@
       </c>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
         <v>33</v>
       </c>
@@ -1432,7 +1556,7 @@
       </c>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>35</v>
       </c>
@@ -1450,7 +1574,7 @@
       </c>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>37</v>
       </c>
@@ -1466,7 +1590,7 @@
       <c r="F14" s="10"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
         <v>38</v>
       </c>
@@ -1484,7 +1608,7 @@
       </c>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="2:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:23" x14ac:dyDescent="0.25">
       <c r="B16" s="9" t="s">
         <v>40</v>
       </c>
@@ -1502,7 +1626,7 @@
       </c>
       <c r="G16" s="11"/>
     </row>
-    <row r="17" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="9" t="s">
         <v>42</v>
       </c>
@@ -1520,7 +1644,7 @@
       </c>
       <c r="G17" s="11"/>
     </row>
-    <row r="18" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="9" t="s">
         <v>44</v>
       </c>
@@ -1538,7 +1662,7 @@
       </c>
       <c r="G18" s="11"/>
     </row>
-    <row r="19" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
         <v>46</v>
       </c>
@@ -1556,7 +1680,7 @@
       </c>
       <c r="G19" s="11"/>
     </row>
-    <row r="20" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="9" t="s">
         <v>48</v>
       </c>
@@ -1574,7 +1698,7 @@
       </c>
       <c r="G20" s="11"/>
     </row>
-    <row r="21" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="9" t="s">
         <v>50</v>
       </c>
@@ -1592,7 +1716,7 @@
       </c>
       <c r="G21" s="11"/>
     </row>
-    <row r="22" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="9" t="s">
         <v>52</v>
       </c>
@@ -1610,7 +1734,7 @@
       </c>
       <c r="G22" s="11"/>
     </row>
-    <row r="23" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
         <v>54</v>
       </c>
@@ -1628,7 +1752,7 @@
       </c>
       <c r="G23" s="11"/>
     </row>
-    <row r="24" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="9" t="s">
         <v>56</v>
       </c>
@@ -1646,7 +1770,7 @@
       </c>
       <c r="G24" s="11"/>
     </row>
-    <row r="25" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="9" t="s">
         <v>58</v>
       </c>
@@ -1664,7 +1788,7 @@
       </c>
       <c r="G25" s="11"/>
     </row>
-    <row r="26" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="9" t="s">
         <v>60</v>
       </c>
@@ -1682,7 +1806,7 @@
       </c>
       <c r="G26" s="11"/>
     </row>
-    <row r="27" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
         <v>62</v>
       </c>
@@ -1700,7 +1824,7 @@
       </c>
       <c r="G27" s="11"/>
     </row>
-    <row r="28" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="9" t="s">
         <v>64</v>
       </c>
@@ -1718,7 +1842,7 @@
       </c>
       <c r="G28" s="11"/>
     </row>
-    <row r="29" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="9" t="s">
         <v>66</v>
       </c>
@@ -1736,7 +1860,7 @@
       </c>
       <c r="G29" s="11"/>
     </row>
-    <row r="30" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>68</v>
       </c>
@@ -1754,7 +1878,7 @@
       </c>
       <c r="G30" s="11"/>
     </row>
-    <row r="31" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
         <v>70</v>
       </c>
@@ -1772,7 +1896,7 @@
       </c>
       <c r="G31" s="11"/>
     </row>
-    <row r="32" spans="2:7" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="9" t="s">
         <v>72</v>
       </c>
@@ -1790,7 +1914,7 @@
       </c>
       <c r="G32" s="11"/>
     </row>
-    <row r="33" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="9" t="s">
         <v>74</v>
       </c>
@@ -1808,7 +1932,7 @@
       </c>
       <c r="G33" s="11"/>
     </row>
-    <row r="34" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="9" t="s">
         <v>76</v>
       </c>
@@ -1826,7 +1950,7 @@
       </c>
       <c r="G34" s="11"/>
     </row>
-    <row r="35" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
         <v>78</v>
       </c>
@@ -1844,7 +1968,7 @@
       </c>
       <c r="G35" s="11"/>
     </row>
-    <row r="36" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="9" t="s">
         <v>80</v>
       </c>
@@ -1862,7 +1986,7 @@
       </c>
       <c r="G36" s="11"/>
     </row>
-    <row r="37" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="9" t="s">
         <v>82</v>
       </c>
@@ -1880,7 +2004,7 @@
       </c>
       <c r="G37" s="11"/>
     </row>
-    <row r="38" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="9" t="s">
         <v>84</v>
       </c>
@@ -1898,7 +2022,7 @@
       </c>
       <c r="G38" s="11"/>
     </row>
-    <row r="39" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
         <v>86</v>
       </c>
@@ -1916,7 +2040,7 @@
       </c>
       <c r="G39" s="11"/>
     </row>
-    <row r="40" spans="2:8" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="9" t="s">
         <v>88</v>
       </c>
@@ -1934,7 +2058,7 @@
       </c>
       <c r="G40" s="11"/>
     </row>
-    <row r="41" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B41" s="9" t="s">
         <v>90</v>
       </c>
@@ -1952,7 +2076,7 @@
       </c>
       <c r="G41" s="11"/>
     </row>
-    <row r="42" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
         <v>16</v>
       </c>
@@ -1969,7 +2093,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="43" spans="2:8" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B43" s="5" t="s">
         <v>119</v>
       </c>
@@ -1986,207 +2110,340 @@
         <v>118</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="F45" s="13"/>
-    </row>
-    <row r="46" spans="2:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B46" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C46" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D46" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F46" s="13"/>
+    <row r="44" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B44" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B45" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B46" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>224</v>
+      </c>
       <c r="H46" s="4"/>
     </row>
-    <row r="47" spans="2:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B47" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>12</v>
+    <row r="47" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B47" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E47" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F47" s="16"/>
-    </row>
-    <row r="48" spans="2:8" ht="15" x14ac:dyDescent="0.2">
-      <c r="B48" s="9" t="s">
-        <v>92</v>
+        <v>6</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B48" s="25" t="s">
+        <v>237</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="F48" s="16"/>
-    </row>
-    <row r="49" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B49" s="9" t="s">
-        <v>111</v>
+        <v>9</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F48" s="23" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B49" s="25" t="s">
+        <v>233</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>13</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E49" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="F49" s="16"/>
-    </row>
-    <row r="50" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B50" s="9" t="s">
-        <v>112</v>
+        <v>9</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B50" s="25" t="s">
+        <v>234</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D50" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="E50" s="15" t="s">
+      <c r="D50" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B51" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E60" s="18"/>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E61" s="18"/>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="E62" s="18"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B66" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="F66" s="13"/>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E67" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="F67" s="16"/>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B68" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E68" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="F68" s="16"/>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="F69" s="16"/>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="E70" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="F50" s="16"/>
-    </row>
-    <row r="51" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B51" s="9" t="s">
+      <c r="F70" s="16"/>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B71" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C71" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D51" s="9" t="s">
+      <c r="D71" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E51" s="15" t="s">
+      <c r="E71" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="F51" s="16"/>
-    </row>
-    <row r="52" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B52" s="9" t="s">
+      <c r="F71" s="16"/>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B72" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C72" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D52" s="9" t="s">
+      <c r="D72" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E52" s="15" t="s">
+      <c r="E72" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="F52" s="16"/>
-    </row>
-    <row r="53" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B53" s="9" t="s">
+      <c r="F72" s="16"/>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B73" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C73" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D53" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E53" s="15" t="s">
+      <c r="D73" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E73" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="F53" s="16"/>
-    </row>
-    <row r="54" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B54" s="9" t="s">
+      <c r="F73" s="16"/>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B74" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C74" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D54" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="E54" s="15" t="s">
+      <c r="D74" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E74" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="F54" s="16"/>
-    </row>
-    <row r="55" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B55" s="9" t="s">
+      <c r="F74" s="16"/>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B75" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C55" s="2" t="s">
+      <c r="C75" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="9" t="s">
+      <c r="D75" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E55" s="15" t="s">
+      <c r="E75" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="F55" s="16"/>
-    </row>
-    <row r="56" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B56" s="9" t="s">
+      <c r="F75" s="16"/>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B76" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C56" s="2" t="s">
+      <c r="C76" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D76" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E56" s="15" t="s">
+      <c r="E76" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="57" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B57" s="9" t="s">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B77" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C57" s="2" t="s">
+      <c r="C77" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D57" s="9" t="s">
+      <c r="D77" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E57" s="15" t="s">
+      <c r="E77" s="15" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="15" x14ac:dyDescent="0.2">
-      <c r="B58" s="9" t="s">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B78" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C78" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D58" s="9" t="s">
+      <c r="D78" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E58" s="15" t="s">
+      <c r="E78" s="15" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="E59" s="18"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="E60" s="18"/>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="E61" s="18"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2235,718 +2492,718 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFD7DAE5-CC87-664E-AAE7-219D6B14F29E}">
   <dimension ref="A1:A145"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="90.6640625" customWidth="1"/>
+    <col min="1" max="1" width="90.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A4" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="21" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="21" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="21" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="21" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="19" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="21" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="20" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="21" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="21" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="21" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="21" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="28" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A28" s="21" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="21"/>
     </row>
-    <row r="30" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="31" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A33" s="21" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="21" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="21" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="42" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="21" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="43" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="44" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="21" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="45" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="21" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="46" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
     </row>
-    <row r="47" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="48" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="49" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="50" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A50" s="21" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="51" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="52" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="21" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="53" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="54" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="21" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="55" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="56" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A56" s="21" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="57" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="58" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="21" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="59" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="21" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="60" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="21" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="21" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="62" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
     </row>
-    <row r="63" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="19" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="64" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="65" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="66" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A66" s="21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="67" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="68" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="21" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="69" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="70" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="21" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="71" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="72" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" s="21" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="73" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="74" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" s="21" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" s="21" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="76" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A76" s="21" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A77" s="21" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:1" ht="31.5" x14ac:dyDescent="0.25">
       <c r="A78" s="21" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="79" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" s="21"/>
     </row>
-    <row r="80" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" s="19" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="81" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" s="20" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="82" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="83" spans="1:1" ht="34" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A83" s="21" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="84" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="86" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="87" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" s="21" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="88" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="89" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" s="21" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="90" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" s="21" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="91" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="92" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" s="21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="93" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="94" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" s="21" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="95" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" s="21" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="96" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" s="21" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" s="21" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="98" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" s="21" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="99" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" s="21" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="100" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" s="21" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="101" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" s="21"/>
     </row>
-    <row r="102" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" s="19" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="103" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" s="20" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="104" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="105" spans="1:1" ht="51" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:1" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A105" s="21" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="106" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="107" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="108" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="109" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" s="21" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="110" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="111" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" s="21" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="112" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="113" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="114" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" s="21" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="115" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="116" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="117" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" s="21" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="118" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" s="21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="119" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" s="21" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="120" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" s="21"/>
     </row>
-    <row r="121" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" s="19" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="122" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" s="20" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="123" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" s="20" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" s="21" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="125" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" s="21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="127" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" s="20" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="128" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" s="21"/>
     </row>
-    <row r="129" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:1" ht="17" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" s="21" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="20" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="132" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="21" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="133" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="21" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="134" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="21" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="135" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="21" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="136" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="21" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="137" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="138" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="21" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="139" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="140" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="21" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="141" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="21" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="142" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="21" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="143" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="21" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="144" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="21" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="145" spans="1:1" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="22" t="s">
         <v>221</v>
       </c>
